--- a/tests/OpdSimulator.Data.Tests/Fixtures/dirty_missing.xlsx
+++ b/tests/OpdSimulator.Data.Tests/Fixtures/dirty_missing.xlsx
@@ -28,37 +28,40 @@
     <x:t>screening_end</x:t>
   </x:si>
   <x:si>
-    <x:t>8:17</x:t>
+    <x:t>8:17:12</x:t>
   </x:si>
   <x:si>
     <x:t>Screening</x:t>
   </x:si>
   <x:si>
-    <x:t>8:18</x:t>
+    <x:t>8:17:58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8:18:12</x:t>
   </x:si>
   <x:si>
     <x:t/>
   </x:si>
   <x:si>
-    <x:t>8:19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8:20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8:21</x:t>
+    <x:t>8:19:48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8:20:04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8:21:16</x:t>
   </x:si>
   <x:si>
     <x:t>Laboratory</x:t>
   </x:si>
   <x:si>
-    <x:t>8:22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8:23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8:24</x:t>
+    <x:t>8:22:09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8:23:13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8:24:08</x:t>
   </x:si>
   <x:si>
     <x:t>9:30</x:t>
@@ -70,10 +73,10 @@
     <x:t>8:00</x:t>
   </x:si>
   <x:si>
-    <x:t>8:26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8:27</x:t>
+    <x:t>8:27:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8:27:34</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -449,80 +452,80 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
